--- a/homework02/数据字典-字典方法说明.xlsx
+++ b/homework02/数据字典-字典方法说明.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\AppData\Local\Kingsoft\WPS Office\12.1.0.28043\office6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\作业仓库\homework02\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="23040" windowHeight="8580"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,6 +35,13 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
@@ -69,6 +76,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Dictionary&lt;string, dynamic&gt; user = new Dictionary&lt;string, dynamic&gt;() {</t>
     </r>
     <r>
@@ -122,6 +137,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Dictionary&lt;string, dynamic&gt; user = new Dictionary&lt;string, dynamic&gt;() { ["name"] = "张三",</t>
     </r>
     <r>
@@ -147,7 +170,7 @@
     </r>
   </si>
   <si>
-    <t>在小括号中放删除的数据的键名</t>
+    <t>在小括号中放删除的数据的键名.</t>
   </si>
   <si>
     <t>Clear</t>
@@ -157,6 +180,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Dictionary&lt;string, dynamic&gt; user = new Dictionary&lt;string, dynamic&gt;() { ["name"] = "张三",</t>
     </r>
     <r>
